--- a/AAII_Financials/Yearly/EFSI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EFSI_YR_FIN.xlsx
@@ -2921,10 +2921,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1607000</v>
+        <v>1607400</v>
       </c>
       <c r="E57" s="3">
-        <v>1574800</v>
+        <v>1575200</v>
       </c>
       <c r="F57" s="3">
         <v>1506100</v>
@@ -2972,10 +2972,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
-        <v>26800</v>
+        <v>26500</v>
       </c>
       <c r="F58" s="3">
         <v>21700</v>
